--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{884B9473-36EF-4628-AB7A-B33BCFF381D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB4A3E80-F33D-43AE-88FE-4CCEB7A1E027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
@@ -310,9 +310,6 @@
     <t>Input Argument</t>
   </si>
   <si>
-    <t>►</t>
-  </si>
-  <si>
     <t>os</t>
   </si>
   <si>
@@ -403,9 +400,6 @@
     <t>_</t>
   </si>
   <si>
-    <t xml:space="preserve"> Overview ↩</t>
-  </si>
-  <si>
     <t>DarkHeader</t>
   </si>
   <si>
@@ -449,6 +443,12 @@
   </si>
   <si>
     <t>https://github.com/InfoDesigner/xleda/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">► </t>
+  </si>
+  <si>
+    <t>Overview →</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="0"/>
@@ -731,6 +731,13 @@
       <b/>
       <i/>
       <sz val="8"/>
+      <color theme="1" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1" tint="0.39997558519241921"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1071,7 +1078,7 @@
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
@@ -1234,13 +1241,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="7" applyFill="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1255,7 +1262,6 @@
     <xf numFmtId="3" fontId="10" fillId="8" borderId="21" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="180"/>
     </xf>
@@ -1273,8 +1279,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1289,16 +1294,15 @@
     <xf numFmtId="3" fontId="21" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="3" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1323,31 +1327,31 @@
     <xf numFmtId="9" fontId="27" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1356,7 +1360,7 @@
     <xf numFmtId="3" fontId="28" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1375,9 +1379,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="34" fillId="5" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1390,14 +1391,16 @@
     <xf numFmtId="3" fontId="10" fillId="2" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="3" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4810,35 +4813,35 @@
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="4.9000000000000004" customHeight="1"/>
+    <row r="1" spans="2:16" ht="5.0999999999999996" customHeight="1"/>
     <row r="2" spans="2:16" ht="20.100000000000001" customHeight="1">
-      <c r="B2" s="119" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="83"/>
-    </row>
-    <row r="3" spans="2:16" ht="10.15" customHeight="1">
-      <c r="B3" s="77"/>
+      <c r="B2" s="114" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="81"/>
+    </row>
+    <row r="3" spans="2:16" ht="10.35" customHeight="1">
+      <c r="B3" s="75"/>
     </row>
     <row r="4" spans="2:16" ht="30" customHeight="1">
-      <c r="B4" s="108" t="e" vm="1">
+      <c r="B4" s="105" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="4.9000000000000004" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="5.0999999999999996" customHeight="1">
       <c r="B5" s="1"/>
       <c r="C5" s="8"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" ht="19.899999999999999" customHeight="1">
+    <row r="6" spans="2:16" ht="20.100000000000001" customHeight="1">
       <c r="B6"/>
       <c r="C6" s="8"/>
       <c r="P6" s="25"/>
     </row>
-    <row r="7" spans="2:16" ht="4.9000000000000004" customHeight="1">
+    <row r="7" spans="2:16" ht="5.0999999999999996" customHeight="1">
       <c r="B7"/>
       <c r="C7" s="8"/>
     </row>
@@ -4866,7 +4869,7 @@
     <row r="10" spans="2:16" ht="15" customHeight="1">
       <c r="C10" s="26"/>
     </row>
-    <row r="11" spans="2:16" ht="19.149999999999999" customHeight="1">
+    <row r="11" spans="2:16" ht="19.350000000000001" customHeight="1">
       <c r="B11"/>
       <c r="C11" s="8"/>
     </row>
@@ -4899,34 +4902,27 @@
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
     <col min="5" max="6" width="27.28515625" customWidth="1"/>
-    <col min="7" max="11" width="19.5703125" customWidth="1"/>
+    <col min="7" max="11" width="19.42578125" customWidth="1"/>
     <col min="12" max="19" width="17.140625" customWidth="1"/>
     <col min="20" max="20" width="20.28515625" customWidth="1"/>
     <col min="21" max="30" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="84" customFormat="1" ht="4.9000000000000004" customHeight="1">
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-    </row>
+    <row r="1" spans="1:28" ht="5.0999999999999996" customHeight="1"/>
     <row r="2" spans="1:28" ht="14.45" customHeight="1">
-      <c r="A2" s="71"/>
-    </row>
-    <row r="3" spans="1:28" s="84" customFormat="1" ht="10.15" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
+      <c r="A2" s="70"/>
+    </row>
+    <row r="3" spans="1:28" ht="10.35" customHeight="1">
+      <c r="A3" s="70"/>
     </row>
     <row r="4" spans="1:28" ht="30" customHeight="1">
-      <c r="B4" s="109" t="e" vm="1">
+      <c r="B4" s="106" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="74"/>
+        <v>84</v>
+      </c>
+      <c r="D4" s="73"/>
       <c r="AB4" s="4"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1">
@@ -4934,11 +4930,11 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28" ht="15" customHeight="1">
-      <c r="B6" s="118" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="119" t="s">
-        <v>95</v>
+      <c r="B6" s="113" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="114" t="s">
+        <v>93</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="43"/>
@@ -4959,80 +4955,80 @@
       <c r="D8" s="43"/>
       <c r="E8" s="43"/>
       <c r="F8" s="43"/>
-      <c r="G8" s="110"/>
+      <c r="G8" s="107"/>
       <c r="K8" s="43"/>
     </row>
-    <row r="9" spans="1:28" s="84" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="C9" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="120"/>
+    <row r="9" spans="1:28" ht="30" hidden="1" customHeight="1">
+      <c r="C9" s="116" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="116"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
-      <c r="G9" s="117"/>
+      <c r="G9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:28" s="84" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="10" spans="1:28" ht="15" hidden="1" customHeight="1">
       <c r="C10" s="43"/>
-      <c r="D10" s="82" t="s">
-        <v>107</v>
+      <c r="D10" s="80" t="s">
+        <v>105</v>
       </c>
       <c r="E10" s="43"/>
       <c r="F10" s="43"/>
-      <c r="G10" s="117"/>
+      <c r="G10" s="43"/>
       <c r="K10" s="43"/>
     </row>
-    <row r="11" spans="1:28" s="84" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="11" spans="1:28" ht="15" hidden="1" customHeight="1">
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
       <c r="F11" s="43"/>
-      <c r="G11" s="117"/>
+      <c r="G11" s="43"/>
       <c r="K11" s="43"/>
     </row>
     <row r="12" spans="1:28" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="120"/>
+      <c r="C12" s="116" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="116"/>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:28" ht="4.9000000000000004" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="13" spans="1:28" ht="5.0999999999999996" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
       <c r="E13" s="43"/>
     </row>
     <row r="14" spans="1:28" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B14" s="41"/>
-      <c r="D14" s="112" t="s">
+      <c r="D14" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="114" t="s">
+      <c r="E14" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="113" t="s">
+      <c r="F14" s="109" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="D15" s="115" t="s">
-        <v>101</v>
+      <c r="D15" s="111" t="s">
+        <v>99</v>
       </c>
       <c r="E15" s="50"/>
       <c r="F15" s="49"/>
     </row>
     <row r="16" spans="1:28" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="D16" s="115" t="s">
-        <v>102</v>
+      <c r="D16" s="111" t="s">
+        <v>100</v>
       </c>
       <c r="E16" s="50"/>
       <c r="F16" s="49"/>
     </row>
     <row r="17" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="D17" s="115" t="s">
+      <c r="D17" s="111" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="50"/>
@@ -5043,110 +5039,110 @@
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
     </row>
-    <row r="19" spans="2:12" ht="10.15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="19" spans="2:12" ht="10.35" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C19" s="43"/>
       <c r="F19" s="43"/>
       <c r="L19" s="38"/>
     </row>
     <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="120"/>
-      <c r="E20" s="80"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="78"/>
       <c r="L20" s="38"/>
     </row>
-    <row r="21" spans="2:12" ht="4.9000000000000004" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="21" spans="2:12" ht="5.0999999999999996" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D21" s="43"/>
       <c r="E21" s="43"/>
     </row>
     <row r="22" spans="2:12" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="D22" s="112" t="s">
+      <c r="D22" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="113" t="s">
+      <c r="E22" s="109" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D23" s="44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" s="56"/>
     </row>
     <row r="24" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D24" s="44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" s="56"/>
     </row>
     <row r="25" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D25" s="44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" s="56"/>
     </row>
     <row r="26" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D26" s="44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" s="56"/>
     </row>
     <row r="27" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D27" s="44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="56"/>
     </row>
     <row r="28" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D28" s="44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" s="56"/>
     </row>
     <row r="29" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D29" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" s="57"/>
     </row>
     <row r="30" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D30" s="44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" s="56"/>
     </row>
     <row r="31" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B31" s="39"/>
       <c r="D31" s="44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="56"/>
     </row>
     <row r="32" spans="2:12" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D32" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="56"/>
     </row>
     <row r="33" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D33" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="56"/>
     </row>
     <row r="34" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D34" s="44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E34" s="56"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="82"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="80"/>
       <c r="K34" s="43"/>
     </row>
     <row r="35" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D35" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E35" s="56"/>
       <c r="K35" s="43"/>
@@ -5155,7 +5151,7 @@
       <c r="B36" s="40"/>
       <c r="C36" s="45"/>
       <c r="D36" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E36" s="56"/>
       <c r="K36" s="43"/>
@@ -5163,7 +5159,7 @@
     <row r="37" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B37" s="40"/>
       <c r="C37" s="45"/>
-      <c r="D37" s="81"/>
+      <c r="D37" s="79"/>
       <c r="E37" s="56"/>
       <c r="K37" s="43"/>
     </row>
@@ -5180,10 +5176,10 @@
       <c r="Y38" s="38"/>
     </row>
     <row r="39" spans="2:25" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C39" s="120" t="s">
+      <c r="C39" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="120"/>
+      <c r="D39" s="116"/>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
       <c r="H39" s="43"/>
@@ -5193,7 +5189,7 @@
       <c r="W39" s="42"/>
       <c r="Y39" s="38"/>
     </row>
-    <row r="40" spans="2:25" ht="4.9000000000000004" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="40" spans="2:25" ht="5.0999999999999996" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D40" s="43"/>
       <c r="E40" s="43"/>
       <c r="F40" s="43"/>
@@ -5206,10 +5202,10 @@
       <c r="Y40" s="38"/>
     </row>
     <row r="41" spans="2:25" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="D41" s="112" t="s">
+      <c r="D41" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="113" t="s">
+      <c r="E41" s="109" t="s">
         <v>55</v>
       </c>
       <c r="F41" s="43"/>
@@ -5223,7 +5219,7 @@
     </row>
     <row r="42" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D42" s="48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E42" s="54"/>
       <c r="F42" s="43"/>
@@ -5237,7 +5233,7 @@
     </row>
     <row r="43" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D43" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E43" s="55"/>
       <c r="F43" s="43"/>
@@ -5251,7 +5247,7 @@
     </row>
     <row r="44" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D44" s="64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="55"/>
       <c r="F44" s="43"/>
@@ -5265,7 +5261,7 @@
     </row>
     <row r="45" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D45" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E45" s="55"/>
       <c r="F45" s="43"/>
@@ -5279,7 +5275,7 @@
     </row>
     <row r="46" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D46" s="64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E46" s="55"/>
       <c r="F46" s="43"/>
@@ -5293,7 +5289,7 @@
     </row>
     <row r="47" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D47" s="64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" s="55"/>
       <c r="F47" s="43"/>
@@ -5307,7 +5303,7 @@
     </row>
     <row r="48" spans="2:25" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D48" s="64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="55"/>
       <c r="F48" s="43"/>
@@ -5321,7 +5317,7 @@
     </row>
     <row r="49" spans="1:31" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D49" s="64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="55"/>
       <c r="F49" s="43"/>
@@ -5335,7 +5331,7 @@
     </row>
     <row r="50" spans="1:31" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D50" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="55"/>
       <c r="F50" s="43"/>
@@ -5349,7 +5345,7 @@
     </row>
     <row r="51" spans="1:31" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D51" s="65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E51" s="66"/>
       <c r="F51" s="43"/>
@@ -5363,7 +5359,7 @@
     </row>
     <row r="52" spans="1:31" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D52" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="55"/>
       <c r="F52" s="43"/>
@@ -5377,7 +5373,7 @@
     </row>
     <row r="53" spans="1:31" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="D53" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E53" s="66"/>
       <c r="F53" s="43"/>
@@ -5403,11 +5399,11 @@
     </row>
     <row r="55" spans="1:31" ht="15" customHeight="1" collapsed="1">
       <c r="A55" s="6"/>
-      <c r="B55" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="111" t="s">
-        <v>87</v>
+      <c r="B55" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="AB55" s="4"/>
     </row>
@@ -5416,177 +5412,176 @@
       <c r="AB56" s="4"/>
     </row>
     <row r="57" spans="1:31" ht="30" customHeight="1">
-      <c r="C57" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57" s="88" t="s">
-        <v>86</v>
-      </c>
-      <c r="E57" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="F57" s="86" t="s">
+      <c r="C57" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="G57" s="87" t="s">
+        <v>6</v>
+      </c>
+      <c r="H57" s="87" t="s">
+        <v>48</v>
+      </c>
+      <c r="I57" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="G57" s="90" t="s">
-        <v>6</v>
-      </c>
-      <c r="H57" s="90" t="s">
-        <v>48</v>
-      </c>
-      <c r="I57" s="90" t="s">
-        <v>90</v>
-      </c>
-      <c r="J57" s="90" t="s">
+      <c r="J57" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="K57" s="86" t="s">
-        <v>98</v>
+      <c r="K57" s="83" t="s">
+        <v>96</v>
       </c>
       <c r="AE57" s="4"/>
     </row>
     <row r="58" spans="1:31" ht="15" customHeight="1">
-      <c r="C58" s="93"/>
-      <c r="D58" s="102"/>
-      <c r="E58" s="103"/>
-      <c r="F58" s="116"/>
-      <c r="G58" s="104"/>
-      <c r="H58" s="105"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="98"/>
-      <c r="K58" s="107"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="99"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="102"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="95"/>
+      <c r="K58" s="104"/>
       <c r="AE58" s="4"/>
     </row>
     <row r="60" spans="1:31" ht="15" customHeight="1">
       <c r="AB60" s="4"/>
     </row>
     <row r="61" spans="1:31" ht="15" customHeight="1">
-      <c r="B61" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="111" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="84"/>
+      <c r="B61" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="AB61" s="4"/>
     </row>
     <row r="62" spans="1:31" ht="20.100000000000001" customHeight="1"/>
-    <row r="63" spans="1:31" ht="10.15" customHeight="1"/>
+    <row r="63" spans="1:31" ht="10.35" customHeight="1"/>
     <row r="64" spans="1:31" ht="30" customHeight="1">
-      <c r="C64" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="91" t="s">
+      <c r="C64" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" s="88" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="F64" s="91" t="s">
+      <c r="F64" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="G64" s="91" t="s">
+      <c r="G64" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H64" s="86" t="s">
+      <c r="H64" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="I64" s="86" t="s">
+      <c r="I64" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="J64" s="86" t="s">
+      <c r="J64" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="K64" s="86" t="s">
+      <c r="K64" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="L64" s="86" t="s">
+      <c r="L64" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="M64" s="86" t="s">
+      <c r="M64" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="N64" s="86" t="s">
+      <c r="N64" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="O64" s="86" t="s">
+      <c r="O64" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="P64" s="86" t="s">
+      <c r="P64" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="Q64" s="86" t="s">
+      <c r="Q64" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="R64" s="86" t="s">
+      <c r="R64" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="S64" s="86" t="s">
+      <c r="S64" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="T64" s="86" t="s">
+      <c r="T64" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="U64" s="86" t="s">
+      <c r="U64" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="V64" s="86" t="s">
+      <c r="V64" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="W64" s="92" t="s">
+      <c r="W64" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="X64" s="92" t="s">
+      <c r="X64" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="Y64" s="92" t="s">
+      <c r="Y64" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="Z64" s="92" t="s">
+      <c r="Z64" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="AA64" s="92" t="s">
+      <c r="AA64" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="AB64" s="86" t="s">
+      <c r="AB64" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="AC64" s="86" t="s">
+      <c r="AC64" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="AD64" s="86" t="s">
+      <c r="AD64" s="83" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="65" spans="3:30" ht="15" customHeight="1">
-      <c r="C65" s="93"/>
-      <c r="D65" s="94"/>
-      <c r="E65" s="95"/>
-      <c r="F65" s="96"/>
-      <c r="G65" s="96"/>
-      <c r="H65" s="97"/>
-      <c r="I65" s="98"/>
-      <c r="J65" s="98"/>
-      <c r="K65" s="98"/>
-      <c r="L65" s="99"/>
-      <c r="M65" s="99"/>
-      <c r="N65" s="99"/>
-      <c r="O65" s="100"/>
-      <c r="P65" s="99"/>
-      <c r="Q65" s="101"/>
-      <c r="R65" s="101"/>
-      <c r="S65" s="101"/>
-      <c r="T65" s="101"/>
-      <c r="U65" s="101"/>
-      <c r="V65" s="101"/>
-      <c r="W65" s="101"/>
-      <c r="X65" s="101"/>
-      <c r="Y65" s="101"/>
-      <c r="Z65" s="101"/>
-      <c r="AA65" s="101"/>
-      <c r="AB65" s="101"/>
-      <c r="AC65" s="101"/>
-      <c r="AD65" s="101"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="93"/>
+      <c r="G65" s="93"/>
+      <c r="H65" s="94"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="95"/>
+      <c r="K65" s="95"/>
+      <c r="L65" s="96"/>
+      <c r="M65" s="96"/>
+      <c r="N65" s="96"/>
+      <c r="O65" s="97"/>
+      <c r="P65" s="96"/>
+      <c r="Q65" s="98"/>
+      <c r="R65" s="98"/>
+      <c r="S65" s="98"/>
+      <c r="T65" s="98"/>
+      <c r="U65" s="98"/>
+      <c r="V65" s="98"/>
+      <c r="W65" s="98"/>
+      <c r="X65" s="98"/>
+      <c r="Y65" s="98"/>
+      <c r="Z65" s="98"/>
+      <c r="AA65" s="98"/>
+      <c r="AB65" s="98"/>
+      <c r="AC65" s="98"/>
+      <c r="AD65" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5689,7 +5684,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF131313"/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="B1:H83"/>
   <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" customHeight="1" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -5699,7 +5694,7 @@
     <col min="5" max="6" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.899999999999999" hidden="1" customHeight="1">
+    <row r="1" spans="2:8" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
       <c r="D1" s="14" t="s">
@@ -5710,96 +5705,82 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:8" s="75" customFormat="1" ht="4.9000000000000004" customHeight="1">
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="119" t="str">
-        <f ca="1">HYPERLINK("#" &amp; CELL("address", _xlfn.XLOOKUP(Name,tbl_DfOverview[Dataframe],tbl_DfOverview[_],tbl_DfOverview[[#Headers],[_]])), "Overview ↩")</f>
-        <v>Overview ↩</v>
-      </c>
-      <c r="C3" s="83"/>
-    </row>
-    <row r="4" spans="1:8" ht="4.9000000000000004" customHeight="1">
-      <c r="B4" s="69"/>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1">
-      <c r="B5" s="108" t="e" vm="1">
+    <row r="2" spans="2:8" ht="5.0999999999999996" customHeight="1">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+    </row>
+    <row r="3" spans="2:8" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="115" t="str">
+        <f ca="1">HYPERLINK("#" &amp; CELL("address", _xlfn.XLOOKUP(Name,tbl_DfOverview[Dataframe],tbl_DfOverview[_],tbl_DfOverview[[#Headers],[_]])), "Overview →")</f>
+        <v>Overview →</v>
+      </c>
+      <c r="C3" s="81"/>
+    </row>
+    <row r="4" spans="2:8" ht="5.0999999999999996" customHeight="1">
+      <c r="B4" s="68"/>
+    </row>
+    <row r="5" spans="2:8" ht="30" customHeight="1">
+      <c r="B5" s="105" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C5" s="78" t="s">
-        <v>99</v>
+      <c r="C5" s="76" t="s">
+        <v>97</v>
       </c>
       <c r="D5" s="22"/>
     </row>
-    <row r="6" spans="1:8" ht="10.15" customHeight="1"/>
-    <row r="7" spans="1:8">
-      <c r="A7" s="67"/>
-      <c r="B7" s="85" t="s">
-        <v>61</v>
+    <row r="6" spans="2:8" ht="10.35" customHeight="1"/>
+    <row r="7" spans="2:8">
+      <c r="B7" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="67"/>
-    </row>
-    <row r="9" spans="1:8" ht="49.9" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="67"/>
-      <c r="D9" s="72" t="s">
+    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1"/>
+    <row r="9" spans="2:8" ht="50.1" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="D9" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="73"/>
-    </row>
-    <row r="10" spans="1:8" hidden="1" outlineLevel="1">
-      <c r="A10" s="67"/>
-    </row>
-    <row r="11" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A11" s="67"/>
+      <c r="E9" s="72"/>
+    </row>
+    <row r="10" spans="2:8" hidden="1" outlineLevel="1"/>
+    <row r="11" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="32"/>
     </row>
-    <row r="12" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A12" s="67"/>
+    <row r="12" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="24"/>
     </row>
-    <row r="13" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A13" s="67"/>
+    <row r="13" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="24"/>
     </row>
-    <row r="14" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A14" s="67"/>
+    <row r="14" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="30"/>
     </row>
-    <row r="15" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A15" s="67"/>
+    <row r="15" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="31"/>
     </row>
-    <row r="16" spans="1:8" ht="10.15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A16" s="67"/>
-    </row>
-    <row r="17" spans="1:6" ht="34.9" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A17" s="67"/>
+    <row r="16" spans="2:8" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
+    <row r="17" spans="2:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C17" s="21" t="s">
         <v>2</v>
       </c>
@@ -5813,10 +5794,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A18" s="67"/>
-    </row>
-    <row r="19" spans="1:6" ht="34.9" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="18" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
+    <row r="19" spans="2:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C19" s="21" t="s">
         <v>3</v>
       </c>
@@ -5830,8 +5809,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="1"/>
-    <row r="21" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" collapsed="1">
+    <row r="20" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
+    <row r="21" spans="2:6" s="23" customFormat="1" ht="30" customHeight="1" collapsed="1">
       <c r="B21" s="58"/>
       <c r="C21" s="58" t="s">
         <v>4</v>
@@ -5840,21 +5819,17 @@
       <c r="E21" s="59"/>
       <c r="F21" s="59"/>
     </row>
-    <row r="22" spans="1:6" ht="10.15" customHeight="1"/>
-    <row r="23" spans="1:6" outlineLevel="1">
-      <c r="A23" s="67"/>
-      <c r="B23" s="85" t="s">
-        <v>61</v>
+    <row r="22" spans="2:6" ht="10.35" customHeight="1"/>
+    <row r="23" spans="2:6" outlineLevel="1">
+      <c r="B23" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
-      <c r="A24" s="67"/>
-    </row>
-    <row r="25" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A25" s="67"/>
+    <row r="24" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
+    <row r="25" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C25" s="19" t="s">
         <v>8</v>
       </c>
@@ -5862,8 +5837,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A26" s="67"/>
+    <row r="26" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
@@ -5871,8 +5845,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A27" s="67"/>
+    <row r="27" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C27" s="18" t="s">
         <v>10</v>
       </c>
@@ -5880,8 +5853,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A28" s="67"/>
+    <row r="28" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C28" s="18" t="s">
         <v>11</v>
       </c>
@@ -5889,8 +5861,7 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A29" s="67"/>
+    <row r="29" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C29" s="18" t="s">
         <v>12</v>
       </c>
@@ -5898,8 +5869,7 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
     </row>
-    <row r="30" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A30" s="67"/>
+    <row r="30" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C30" s="18" t="s">
         <v>13</v>
       </c>
@@ -5907,8 +5877,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
     </row>
-    <row r="31" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A31" s="67"/>
+    <row r="31" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C31" s="19" t="s">
         <v>14</v>
       </c>
@@ -5916,8 +5885,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
     </row>
-    <row r="32" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A32" s="67"/>
+    <row r="32" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
@@ -5925,25 +5893,19 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
     </row>
-    <row r="33" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A33" s="67"/>
-    </row>
-    <row r="34" spans="1:6" ht="124.9" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="35" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="36" spans="1:6" outlineLevel="1" collapsed="1">
-      <c r="A36" s="67"/>
-      <c r="B36" s="85" t="s">
-        <v>61</v>
+    <row r="33" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="34" spans="2:6" ht="125.1" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="35" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="36" spans="2:6" outlineLevel="1" collapsed="1">
+      <c r="B36" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
-      <c r="A37" s="67"/>
-    </row>
-    <row r="38" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A38" s="67"/>
+    <row r="37" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
+    <row r="38" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C38" s="3" t="s">
         <v>17</v>
       </c>
@@ -5951,8 +5913,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A39" s="67"/>
+    <row r="39" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C39" s="18" t="s">
         <v>18</v>
       </c>
@@ -5960,8 +5921,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A40" s="67"/>
+    <row r="40" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
@@ -5969,8 +5929,7 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A41" s="67"/>
+    <row r="41" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C41" s="3" t="s">
         <v>20</v>
       </c>
@@ -5978,8 +5937,7 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A42" s="67"/>
+    <row r="42" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C42" s="20" t="s">
         <v>21</v>
       </c>
@@ -5987,25 +5945,19 @@
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
     </row>
-    <row r="43" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A43" s="67"/>
-    </row>
-    <row r="44" spans="1:6" ht="150" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="45" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="46" spans="1:6" outlineLevel="1" collapsed="1">
-      <c r="A46" s="67"/>
-      <c r="B46" s="85" t="s">
-        <v>61</v>
+    <row r="43" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="44" spans="2:6" ht="150" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="45" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="46" spans="2:6" outlineLevel="1" collapsed="1">
+      <c r="B46" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
-      <c r="A47" s="67"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A48" s="67"/>
+    <row r="47" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
+    <row r="48" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
@@ -6013,8 +5965,7 @@
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
     </row>
-    <row r="49" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A49" s="67"/>
+    <row r="49" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C49" s="18">
         <v>0.05</v>
       </c>
@@ -6022,8 +5973,7 @@
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
     </row>
-    <row r="50" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A50" s="67"/>
+    <row r="50" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C50" s="19">
         <v>0.25</v>
       </c>
@@ -6031,8 +5981,7 @@
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
     </row>
-    <row r="51" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A51" s="67"/>
+    <row r="51" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C51" s="3">
         <v>0.5</v>
       </c>
@@ -6040,8 +5989,7 @@
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
     </row>
-    <row r="52" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A52" s="67"/>
+    <row r="52" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C52" s="18">
         <v>0.75</v>
       </c>
@@ -6049,8 +5997,7 @@
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
     </row>
-    <row r="53" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A53" s="67"/>
+    <row r="53" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C53" s="18">
         <v>0.95</v>
       </c>
@@ -6058,8 +6005,7 @@
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
     </row>
-    <row r="54" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A54" s="67"/>
+    <row r="54" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C54" s="3" t="s">
         <v>24</v>
       </c>
@@ -6067,8 +6013,7 @@
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
     </row>
-    <row r="55" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A55" s="67"/>
+    <row r="55" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C55" s="18" t="s">
         <v>25</v>
       </c>
@@ -6076,7 +6021,7 @@
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
     </row>
-    <row r="56" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="56" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C56" s="3" t="s">
         <v>26</v>
       </c>
@@ -6084,21 +6029,17 @@
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
     </row>
-    <row r="57" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="58" spans="1:6" outlineLevel="1" collapsed="1">
-      <c r="A58" s="67"/>
-      <c r="B58" s="85" t="s">
-        <v>61</v>
+    <row r="57" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="58" spans="2:6" outlineLevel="1" collapsed="1">
+      <c r="B58" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
-      <c r="A59" s="67"/>
-    </row>
-    <row r="60" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A60" s="67"/>
+    <row r="59" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
+    <row r="60" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C60" s="3" t="s">
         <v>28</v>
       </c>
@@ -6112,8 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A61" s="67"/>
+    <row r="61" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C61" s="18" t="s">
         <v>29</v>
       </c>
@@ -6127,8 +6067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A62" s="67"/>
+    <row r="62" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C62" s="18" t="s">
         <v>30</v>
       </c>
@@ -6142,8 +6081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A63" s="67"/>
+    <row r="63" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C63" s="18" t="s">
         <v>31</v>
       </c>
@@ -6157,8 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A64" s="67"/>
+    <row r="64" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C64" s="3" t="s">
         <v>32</v>
       </c>
@@ -6172,8 +6109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A65" s="67"/>
+    <row r="65" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C65" s="18" t="s">
         <v>33</v>
       </c>
@@ -6187,8 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A66" s="67"/>
+    <row r="66" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C66" s="18" t="s">
         <v>34</v>
       </c>
@@ -6202,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="67" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C67" s="3" t="s">
         <v>35</v>
       </c>
@@ -6216,21 +6151,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="69" spans="1:6" outlineLevel="1" collapsed="1">
-      <c r="A69" s="67"/>
-      <c r="B69" s="85" t="s">
-        <v>61</v>
+    <row r="68" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="69" spans="2:6" outlineLevel="1" collapsed="1">
+      <c r="B69" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
-      <c r="A70" s="67"/>
-    </row>
-    <row r="71" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A71" s="67"/>
+    <row r="70" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
+    <row r="71" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C71" s="3" t="str">
         <f>IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C60)," ","_") &amp;" = ")</f>
         <v/>
@@ -6240,8 +6171,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A72" s="67"/>
+    <row r="72" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C72" s="17" t="str">
         <f>IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C61)," ","_")&amp;" = ")</f>
         <v/>
@@ -6251,8 +6181,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A73" s="67"/>
+    <row r="73" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C73" s="17" t="str">
         <f>IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C62)," ","_")&amp;" = ")</f>
         <v/>
@@ -6262,8 +6191,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A74" s="67"/>
+    <row r="74" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C74" s="17" t="str">
         <f>IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C63)," ","_")&amp;" = ")</f>
         <v/>
@@ -6273,8 +6201,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A75" s="67"/>
+    <row r="75" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C75" s="17" t="str">
         <f>IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C64)," ","_")&amp;" = ")</f>
         <v/>
@@ -6284,8 +6211,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A76" s="67"/>
+    <row r="76" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C76" s="17" t="str">
         <f>IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C65)," ","_")&amp;" = ")</f>
         <v/>
@@ -6295,8 +6221,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A77" s="67"/>
+    <row r="77" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C77" s="16" t="str">
         <f>IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C66)," ","_")&amp;" = ")</f>
         <v/>
@@ -6306,8 +6231,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
-      <c r="A78" s="67"/>
+    <row r="78" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C78" s="3" t="str">
         <f>IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C67)," ","_")&amp;" = ")</f>
         <v/>
@@ -6317,7 +6241,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="79" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C79" s="15" t="str">
         <f>IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(LightHeader)," ", "_") &amp;" = ")</f>
         <v/>
@@ -6327,19 +6251,19 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="10.15" hidden="1" customHeight="1" outlineLevel="1" collapsed="1"/>
+    <row r="80" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1" collapsed="1"/>
     <row r="81" spans="3:6" ht="30" customHeight="1">
       <c r="C81" s="62" t="s">
         <v>37</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E81" s="60" t="s">
         <v>38</v>
       </c>
       <c r="F81" s="60" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="3:6" ht="15" customHeight="1">
@@ -6347,15 +6271,15 @@
         <v>0</v>
       </c>
       <c r="D82" s="61"/>
-      <c r="E82" s="79"/>
+      <c r="E82" s="77"/>
       <c r="F82" s="61"/>
     </row>
     <row r="83" spans="3:6" ht="15" customHeight="1">
-      <c r="C83" s="70" t="b">
+      <c r="C83" s="69" t="b">
         <v>0</v>
       </c>
       <c r="D83" s="61"/>
-      <c r="E83" s="79"/>
+      <c r="E83" s="77"/>
       <c r="F83" s="61"/>
     </row>
   </sheetData>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB4A3E80-F33D-43AE-88FE-4CCEB7A1E027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27416712-FCEE-487F-83CE-CBB073D1063A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
@@ -1078,7 +1078,7 @@
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
@@ -1403,6 +1403,7 @@
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="32" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4899,7 +4900,7 @@
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
     <col min="5" max="6" width="27.28515625" customWidth="1"/>
     <col min="7" max="11" width="19.42578125" customWidth="1"/>
@@ -4909,10 +4910,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="5.0999999999999996" customHeight="1"/>
-    <row r="2" spans="1:28" ht="14.45" customHeight="1">
+    <row r="2" spans="1:28" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="70"/>
     </row>
-    <row r="3" spans="1:28" ht="10.35" customHeight="1">
+    <row r="3" spans="1:28" ht="5.0999999999999996" customHeight="1">
       <c r="A3" s="70"/>
     </row>
     <row r="4" spans="1:28" ht="30" customHeight="1">
@@ -4925,7 +4926,7 @@
       <c r="D4" s="73"/>
       <c r="AB4" s="4"/>
     </row>
-    <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:28" ht="10.35" customHeight="1">
       <c r="C5" s="53"/>
       <c r="AB5" s="4"/>
     </row>
@@ -4959,10 +4960,10 @@
       <c r="K8" s="43"/>
     </row>
     <row r="9" spans="1:28" ht="30" hidden="1" customHeight="1">
-      <c r="C9" s="116" t="s">
+      <c r="C9" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="116"/>
+      <c r="D9" s="117"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -4988,10 +4989,10 @@
     </row>
     <row r="12" spans="1:28" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="117"/>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
       <c r="K12" s="43"/>
@@ -5045,10 +5046,10 @@
       <c r="L19" s="38"/>
     </row>
     <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C20" s="116" t="s">
+      <c r="C20" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="116"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="78"/>
       <c r="L20" s="38"/>
     </row>
@@ -5176,10 +5177,10 @@
       <c r="Y38" s="38"/>
     </row>
     <row r="39" spans="2:25" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C39" s="116" t="s">
+      <c r="C39" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="116"/>
+      <c r="D39" s="117"/>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
       <c r="H39" s="43"/>
@@ -5684,7 +5685,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF131313"/>
   </sheetPr>
-  <dimension ref="B1:H83"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" customHeight="1" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -5694,7 +5695,7 @@
     <col min="5" max="6" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="1" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
       <c r="D1" s="14" t="s">
@@ -5705,7 +5706,7 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="2:8" ht="5.0999999999999996" customHeight="1">
+    <row r="2" spans="1:8" ht="5.0999999999999996" customHeight="1">
       <c r="C2" s="74"/>
       <c r="D2" s="74"/>
       <c r="E2" s="74"/>
@@ -5713,17 +5714,17 @@
       <c r="G2" s="74"/>
       <c r="H2" s="74"/>
     </row>
-    <row r="3" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="115" t="str">
         <f ca="1">HYPERLINK("#" &amp; CELL("address", _xlfn.XLOOKUP(Name,tbl_DfOverview[Dataframe],tbl_DfOverview[_],tbl_DfOverview[[#Headers],[_]])), "Overview →")</f>
         <v>Overview →</v>
       </c>
       <c r="C3" s="81"/>
     </row>
-    <row r="4" spans="2:8" ht="5.0999999999999996" customHeight="1">
+    <row r="4" spans="1:8" ht="5.0999999999999996" customHeight="1">
       <c r="B4" s="68"/>
     </row>
-    <row r="5" spans="2:8" ht="30" customHeight="1">
+    <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="B5" s="105" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -5732,8 +5733,9 @@
       </c>
       <c r="D5" s="22"/>
     </row>
-    <row r="6" spans="2:8" ht="10.35" customHeight="1"/>
-    <row r="7" spans="2:8">
+    <row r="6" spans="1:8" ht="10.35" customHeight="1"/>
+    <row r="7" spans="1:8">
+      <c r="A7" s="116"/>
       <c r="B7" s="82" t="s">
         <v>106</v>
       </c>
@@ -5741,46 +5743,59 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1"/>
-    <row r="9" spans="2:8" ht="50.1" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="116"/>
+    </row>
+    <row r="9" spans="1:8" ht="50.1" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A9" s="116"/>
       <c r="D9" s="71" t="s">
         <v>51</v>
       </c>
       <c r="E9" s="72"/>
     </row>
-    <row r="10" spans="2:8" hidden="1" outlineLevel="1"/>
-    <row r="11" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1">
+      <c r="A10" s="116"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A11" s="116"/>
       <c r="C11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="32"/>
     </row>
-    <row r="12" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="12" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A12" s="116"/>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="24"/>
     </row>
-    <row r="13" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="13" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A13" s="116"/>
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="24"/>
     </row>
-    <row r="14" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="14" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A14" s="116"/>
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="30"/>
     </row>
-    <row r="15" spans="2:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="15" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A15" s="116"/>
       <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="31"/>
     </row>
-    <row r="16" spans="2:8" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
-    <row r="17" spans="2:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="16" spans="1:8" ht="10.35" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A16" s="116"/>
+    </row>
+    <row r="17" spans="1:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A17" s="116"/>
       <c r="C17" s="21" t="s">
         <v>2</v>
       </c>
@@ -5794,8 +5809,10 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
-    <row r="19" spans="2:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="18" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A18" s="116"/>
+    </row>
+    <row r="19" spans="1:6" ht="35.1" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C19" s="21" t="s">
         <v>3</v>
       </c>
@@ -5809,8 +5826,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
-    <row r="21" spans="2:6" s="23" customFormat="1" ht="30" customHeight="1" collapsed="1">
+    <row r="20" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1"/>
+    <row r="21" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" collapsed="1">
       <c r="B21" s="58"/>
       <c r="C21" s="58" t="s">
         <v>4</v>
@@ -5819,8 +5836,9 @@
       <c r="E21" s="59"/>
       <c r="F21" s="59"/>
     </row>
-    <row r="22" spans="2:6" ht="10.35" customHeight="1"/>
-    <row r="23" spans="2:6" outlineLevel="1">
+    <row r="22" spans="1:6" ht="10.35" customHeight="1"/>
+    <row r="23" spans="1:6" outlineLevel="1">
+      <c r="A23" s="116"/>
       <c r="B23" s="82" t="s">
         <v>106</v>
       </c>
@@ -5828,8 +5846,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
-    <row r="25" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
+      <c r="A24" s="116"/>
+    </row>
+    <row r="25" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A25" s="116"/>
       <c r="C25" s="19" t="s">
         <v>8</v>
       </c>
@@ -5837,7 +5858,8 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="26" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A26" s="116"/>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
@@ -5845,7 +5867,8 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="27" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A27" s="116"/>
       <c r="C27" s="18" t="s">
         <v>10</v>
       </c>
@@ -5853,7 +5876,8 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="28" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A28" s="116"/>
       <c r="C28" s="18" t="s">
         <v>11</v>
       </c>
@@ -5861,7 +5885,8 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="29" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A29" s="116"/>
       <c r="C29" s="18" t="s">
         <v>12</v>
       </c>
@@ -5869,7 +5894,8 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
     </row>
-    <row r="30" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="30" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A30" s="116"/>
       <c r="C30" s="18" t="s">
         <v>13</v>
       </c>
@@ -5877,7 +5903,8 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
     </row>
-    <row r="31" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="31" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A31" s="116"/>
       <c r="C31" s="19" t="s">
         <v>14</v>
       </c>
@@ -5885,7 +5912,8 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
     </row>
-    <row r="32" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="32" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A32" s="116"/>
       <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
@@ -5893,10 +5921,13 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
     </row>
-    <row r="33" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="34" spans="2:6" ht="125.1" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="35" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="36" spans="2:6" outlineLevel="1" collapsed="1">
+    <row r="33" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A33" s="116"/>
+    </row>
+    <row r="34" spans="1:6" ht="125.1" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="35" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="36" spans="1:6" outlineLevel="1" collapsed="1">
+      <c r="A36" s="116"/>
       <c r="B36" s="82" t="s">
         <v>106</v>
       </c>
@@ -5904,8 +5935,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
-    <row r="38" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
+      <c r="A37" s="116"/>
+    </row>
+    <row r="38" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A38" s="116"/>
       <c r="C38" s="3" t="s">
         <v>17</v>
       </c>
@@ -5913,7 +5947,8 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="39" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A39" s="116"/>
       <c r="C39" s="18" t="s">
         <v>18</v>
       </c>
@@ -5921,7 +5956,8 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="40" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A40" s="116"/>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
@@ -5929,7 +5965,8 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A41" s="116"/>
       <c r="C41" s="3" t="s">
         <v>20</v>
       </c>
@@ -5937,7 +5974,8 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="42" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A42" s="116"/>
       <c r="C42" s="20" t="s">
         <v>21</v>
       </c>
@@ -5945,10 +5983,13 @@
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
     </row>
-    <row r="43" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="44" spans="2:6" ht="150" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="45" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="46" spans="2:6" outlineLevel="1" collapsed="1">
+    <row r="43" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A43" s="116"/>
+    </row>
+    <row r="44" spans="1:6" ht="150" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="45" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="46" spans="1:6" outlineLevel="1" collapsed="1">
+      <c r="A46" s="116"/>
       <c r="B46" s="82" t="s">
         <v>106</v>
       </c>
@@ -5956,8 +5997,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
-    <row r="48" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
+      <c r="A47" s="116"/>
+    </row>
+    <row r="48" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A48" s="116"/>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
@@ -5965,7 +6009,8 @@
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
     </row>
-    <row r="49" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="49" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A49" s="116"/>
       <c r="C49" s="18">
         <v>0.05</v>
       </c>
@@ -5973,7 +6018,8 @@
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
     </row>
-    <row r="50" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="50" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A50" s="116"/>
       <c r="C50" s="19">
         <v>0.25</v>
       </c>
@@ -5981,7 +6027,8 @@
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
     </row>
-    <row r="51" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="51" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A51" s="116"/>
       <c r="C51" s="3">
         <v>0.5</v>
       </c>
@@ -5989,7 +6036,8 @@
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
     </row>
-    <row r="52" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="52" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A52" s="116"/>
       <c r="C52" s="18">
         <v>0.75</v>
       </c>
@@ -5997,7 +6045,8 @@
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
     </row>
-    <row r="53" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="53" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A53" s="116"/>
       <c r="C53" s="18">
         <v>0.95</v>
       </c>
@@ -6005,7 +6054,8 @@
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
     </row>
-    <row r="54" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="54" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A54" s="116"/>
       <c r="C54" s="3" t="s">
         <v>24</v>
       </c>
@@ -6013,7 +6063,8 @@
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
     </row>
-    <row r="55" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="55" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A55" s="116"/>
       <c r="C55" s="18" t="s">
         <v>25</v>
       </c>
@@ -6021,7 +6072,7 @@
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
     </row>
-    <row r="56" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="56" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C56" s="3" t="s">
         <v>26</v>
       </c>
@@ -6029,8 +6080,9 @@
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
     </row>
-    <row r="57" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="58" spans="2:6" outlineLevel="1" collapsed="1">
+    <row r="57" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="58" spans="1:6" outlineLevel="1" collapsed="1">
+      <c r="A58" s="116"/>
       <c r="B58" s="82" t="s">
         <v>106</v>
       </c>
@@ -6038,8 +6090,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
-    <row r="60" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="59" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
+      <c r="A59" s="116"/>
+    </row>
+    <row r="60" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A60" s="116"/>
       <c r="C60" s="3" t="s">
         <v>28</v>
       </c>
@@ -6053,7 +6108,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="61" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A61" s="116"/>
       <c r="C61" s="18" t="s">
         <v>29</v>
       </c>
@@ -6067,7 +6123,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="62" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A62" s="116"/>
       <c r="C62" s="18" t="s">
         <v>30</v>
       </c>
@@ -6081,7 +6138,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="63" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A63" s="116"/>
       <c r="C63" s="18" t="s">
         <v>31</v>
       </c>
@@ -6095,7 +6153,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="64" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A64" s="116"/>
       <c r="C64" s="3" t="s">
         <v>32</v>
       </c>
@@ -6109,7 +6168,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="65" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A65" s="116"/>
       <c r="C65" s="18" t="s">
         <v>33</v>
       </c>
@@ -6123,7 +6183,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="66" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A66" s="116"/>
       <c r="C66" s="18" t="s">
         <v>34</v>
       </c>
@@ -6137,7 +6198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="67" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C67" s="3" t="s">
         <v>35</v>
       </c>
@@ -6151,8 +6212,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
-    <row r="69" spans="2:6" outlineLevel="1" collapsed="1">
+    <row r="68" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="2"/>
+    <row r="69" spans="1:6" outlineLevel="1" collapsed="1">
+      <c r="A69" s="116"/>
       <c r="B69" s="82" t="s">
         <v>106</v>
       </c>
@@ -6160,8 +6222,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="2:6" ht="20.100000000000001" customHeight="1" outlineLevel="1"/>
-    <row r="71" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="70" spans="1:6" ht="20.100000000000001" customHeight="1" outlineLevel="1">
+      <c r="A70" s="116"/>
+    </row>
+    <row r="71" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A71" s="116"/>
       <c r="C71" s="3" t="str">
         <f>IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C60)," ","_") &amp;" = ")</f>
         <v/>
@@ -6171,7 +6236,8 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="72" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A72" s="116"/>
       <c r="C72" s="17" t="str">
         <f>IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C61)," ","_")&amp;" = ")</f>
         <v/>
@@ -6181,7 +6247,8 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="73" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A73" s="116"/>
       <c r="C73" s="17" t="str">
         <f>IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C62)," ","_")&amp;" = ")</f>
         <v/>
@@ -6191,7 +6258,8 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="74" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A74" s="116"/>
       <c r="C74" s="17" t="str">
         <f>IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C63)," ","_")&amp;" = ")</f>
         <v/>
@@ -6201,7 +6269,8 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="75" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A75" s="116"/>
       <c r="C75" s="17" t="str">
         <f>IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C64)," ","_")&amp;" = ")</f>
         <v/>
@@ -6211,7 +6280,8 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="76" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A76" s="116"/>
       <c r="C76" s="17" t="str">
         <f>IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C65)," ","_")&amp;" = ")</f>
         <v/>
@@ -6221,7 +6291,8 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="77" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A77" s="116"/>
       <c r="C77" s="16" t="str">
         <f>IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C66)," ","_")&amp;" = ")</f>
         <v/>
@@ -6231,7 +6302,8 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="78" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+      <c r="A78" s="116"/>
       <c r="C78" s="3" t="str">
         <f>IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(C67)," ","_")&amp;" = ")</f>
         <v/>
@@ -6241,7 +6313,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
+    <row r="79" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="2">
       <c r="C79" s="15" t="str">
         <f>IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"",SUBSTITUTE(LOWER(LightHeader)," ", "_") &amp;" = ")</f>
         <v/>
@@ -6251,7 +6323,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1" collapsed="1"/>
+    <row r="80" spans="1:6" ht="10.35" hidden="1" customHeight="1" outlineLevel="1" collapsed="1"/>
     <row r="81" spans="3:6" ht="30" customHeight="1">
       <c r="C81" s="62" t="s">
         <v>37</v>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27416712-FCEE-487F-83CE-CBB073D1063A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04CF3C4B-FB60-4DCF-A316-964642143F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04CF3C4B-FB60-4DCF-A316-964642143F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB6E55A-D86D-4ECE-8BA0-4CD7D5145F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB6E55A-D86D-4ECE-8BA0-4CD7D5145F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2FAB45D-FC70-4A6C-A1D7-A0D1262DF5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2FAB45D-FC70-4A6C-A1D7-A0D1262DF5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F89DBD8E-BA47-4985-A545-B8502F226EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F89DBD8E-BA47-4985-A545-B8502F226EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F287A0B-C783-42E4-9383-4C5F05488284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F287A0B-C783-42E4-9383-4C5F05488284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB782DB-F52E-4735-BFE1-D6AB23CCF045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB782DB-F52E-4735-BFE1-D6AB23CCF045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DEC2917-5243-4B12-BB72-D67C3A2954B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
@@ -54,6 +54,7 @@
     <definedName name="Name" localSheetId="0">SinglePlot!$C$4</definedName>
     <definedName name="Notes" localSheetId="2">'Field Analysis'!$D$19:$F$19</definedName>
     <definedName name="Percentiles" localSheetId="2">'Field Analysis'!$C$48:$C$57</definedName>
+    <definedName name="PythonList">_xlfn.LAMBDA(_xlpm.rng,     "[" &amp;      _xlfn.TEXTJOIN(", ", TRUE,          _xlfn.MAP(_xlpm.rng, _xlfn.LAMBDA(_xlpm.cell,             IF(OR(ISERROR(_xlpm.cell), ISBLANK(_xlpm.cell)), "''",             IF(ISLOGICAL(_xlpm.cell), IF(_xlpm.cell, "True", "False"),             IF(ISNUMBER(_xlpm.cell), _xlpm.cell,             "'" &amp; SUBSTITUTE(_xlpm.cell, "'", "\'") &amp; "'"             )))         ))     ) &amp;      "]" )</definedName>
     <definedName name="SerializedLists" localSheetId="2">'Field Analysis'!$D$71:$D$80</definedName>
     <definedName name="SinglePlot" localSheetId="0">SinglePlot!$C$10</definedName>
     <definedName name="Summary_Stats" localSheetId="2">'Field Analysis'!$C$38:$C$45</definedName>
@@ -6232,7 +6233,7 @@
         <v/>
       </c>
       <c r="D71" t="str" cm="1">
-        <f t="array" ref="D71">IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList1&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D71">IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList1&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6243,7 +6244,7 @@
         <v/>
       </c>
       <c r="D72" t="str" cm="1">
-        <f t="array" ref="D72">IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList2&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D72">IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList2&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6254,7 +6255,7 @@
         <v/>
       </c>
       <c r="D73" t="str" cm="1">
-        <f t="array" ref="D73">IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList3&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D73">IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList3&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6265,7 +6266,7 @@
         <v/>
       </c>
       <c r="D74" t="str" cm="1">
-        <f t="array" ref="D74">IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList4&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D74">IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList4&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6276,7 +6277,7 @@
         <v/>
       </c>
       <c r="D75" t="str" cm="1">
-        <f t="array" ref="D75">IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList5&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D75">IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList5&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6287,7 +6288,7 @@
         <v/>
       </c>
       <c r="D76" t="str" cm="1">
-        <f t="array" ref="D76">IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList6&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D76">IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList6&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6298,7 +6299,7 @@
         <v/>
       </c>
       <c r="D77" t="str" cm="1">
-        <f t="array" ref="D77">IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList7&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D77">IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList7&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6309,7 +6310,7 @@
         <v/>
       </c>
       <c r="D78" t="str" cm="1">
-        <f t="array" ref="D78">IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList8&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D78">IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList8&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6319,7 +6320,7 @@
         <v/>
       </c>
       <c r="D79" t="str" cm="1">
-        <f t="array" ref="D79">IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(_xlfn.TAKE(tbl_SourceData[],,-1), tbl_SourceData[Record List] &lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D79">IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(_xlfn.TAKE(tbl_SourceData[],,-1), tbl_SourceData[Record List] &lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB782DB-F52E-4735-BFE1-D6AB23CCF045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B025F63-C475-40D8-9EDC-409F212BDAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
@@ -54,6 +54,7 @@
     <definedName name="Name" localSheetId="0">SinglePlot!$C$4</definedName>
     <definedName name="Notes" localSheetId="2">'Field Analysis'!$D$19:$F$19</definedName>
     <definedName name="Percentiles" localSheetId="2">'Field Analysis'!$C$48:$C$57</definedName>
+    <definedName name="PythonList">_xlfn.LAMBDA(_xlpm.rng,     "[" &amp;      _xlfn.TEXTJOIN(", ", TRUE,          _xlfn.MAP(_xlpm.rng, _xlfn.LAMBDA(_xlpm.cell,             IF(OR(ISERROR(_xlpm.cell), ISBLANK(_xlpm.cell)), "''",             IF(ISLOGICAL(_xlpm.cell), IF(_xlpm.cell, "True", "False"),             IF(ISNUMBER(_xlpm.cell), _xlpm.cell,             "'" &amp; SUBSTITUTE(_xlpm.cell, "'", "\'") &amp; "'"             )))         ))     ) &amp;      "]" )</definedName>
     <definedName name="SerializedLists" localSheetId="2">'Field Analysis'!$D$71:$D$80</definedName>
     <definedName name="SinglePlot" localSheetId="0">SinglePlot!$C$10</definedName>
     <definedName name="Summary_Stats" localSheetId="2">'Field Analysis'!$C$38:$C$45</definedName>
@@ -6232,7 +6233,7 @@
         <v/>
       </c>
       <c r="D71" t="str" cm="1">
-        <f t="array" ref="D71">IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList1&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D71">IF(COUNTIF(FieldList1, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList1&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6243,7 +6244,7 @@
         <v/>
       </c>
       <c r="D72" t="str" cm="1">
-        <f t="array" ref="D72">IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList2&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D72">IF(COUNTIF(FieldList2, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList2&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6254,7 +6255,7 @@
         <v/>
       </c>
       <c r="D73" t="str" cm="1">
-        <f t="array" ref="D73">IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList3&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D73">IF(COUNTIF(FieldList3, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList3&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6265,7 +6266,7 @@
         <v/>
       </c>
       <c r="D74" t="str" cm="1">
-        <f t="array" ref="D74">IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList4&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D74">IF(COUNTIF(FieldList4, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList4&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6276,7 +6277,7 @@
         <v/>
       </c>
       <c r="D75" t="str" cm="1">
-        <f t="array" ref="D75">IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList5&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D75">IF(COUNTIF(FieldList5, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList5&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6287,7 +6288,7 @@
         <v/>
       </c>
       <c r="D76" t="str" cm="1">
-        <f t="array" ref="D76">IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList6&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D76">IF(COUNTIF(FieldList6, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList6&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6298,7 +6299,7 @@
         <v/>
       </c>
       <c r="D77" t="str" cm="1">
-        <f t="array" ref="D77">IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList7&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D77">IF(COUNTIF(FieldList7, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList7&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6309,7 +6310,7 @@
         <v/>
       </c>
       <c r="D78" t="str" cm="1">
-        <f t="array" ref="D78">IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(FieldRange,FieldList8&lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D78">IF(COUNTIF(FieldList8, "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(FieldRange,FieldList8&lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>
@@ -6319,7 +6320,7 @@
         <v/>
       </c>
       <c r="D79" t="str" cm="1">
-        <f t="array" ref="D79">IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"","['"&amp;_xlfn.TEXTJOIN("', '", TRUE, _xlfn._xlws.FILTER(_xlfn.TAKE(tbl_SourceData[],,-1), tbl_SourceData[Record List] &lt;&gt; FALSE, ""))&amp;"']")</f>
+        <f t="array" ref="D79">IF(COUNTIF(tbl_SourceData[Record List], "&lt;&gt;FALSE") = 0,"",PythonList(_xlfn._xlws.FILTER(_xlfn.TAKE(tbl_SourceData[],,-1), tbl_SourceData[Record List] &lt;&gt; FALSE, "")))</f>
         <v/>
       </c>
     </row>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D35A175E-75D5-4378-84EC-66C152AFF666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC2DEB98-31D2-4716-826C-F95AC4C57A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC2DEB98-31D2-4716-826C-F95AC4C57A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AE9F010-AD78-4E0C-A790-C8D6CE64E4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AE9F010-AD78-4E0C-A790-C8D6CE64E4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9CC43DF-5C5E-47CD-8BBF-4FD38ABA3EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9CC43DF-5C5E-47CD-8BBF-4FD38ABA3EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C49ACB-CF52-467E-9AEF-4DA6EABBCD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C49ACB-CF52-467E-9AEF-4DA6EABBCD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{700678EF-98B6-45CB-B5E8-987092382BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{700678EF-98B6-45CB-B5E8-987092382BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C934E3F0-32AE-4D9D-96A5-0AC7327462E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{700678EF-98B6-45CB-B5E8-987092382BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3F4105E-E3C2-42E9-B470-B8F4A773480A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C934E3F0-32AE-4D9D-96A5-0AC7327462E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D95A053-6B77-495F-8371-78CB2BD28809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED250112-A3C8-450D-AC9F-AE3A490AC52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D418B4E-758D-42C7-91AC-1E88081A2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D418B4E-758D-42C7-91AC-1E88081A2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A535B7-E1AA-41EA-B42A-883290D779F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A535B7-E1AA-41EA-B42A-883290D779F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC1AE00-4C86-4617-8BE2-DEE2DE31F0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A535B7-E1AA-41EA-B42A-883290D779F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1B0EE2F-7F5B-41FC-98DF-B79FAB3F79F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA0E77E4-5AFB-4029-95DB-71E233EF9DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B0B5CD7-3176-44E5-805E-25FDE51BDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B0B5CD7-3176-44E5-805E-25FDE51BDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F54C9E9-4C74-4441-9198-E3B3D33DC6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F54C9E9-4C74-4441-9198-E3B3D33DC6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A434101E-201B-48FF-AF81-F886884EC64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A434101E-201B-48FF-AF81-F886884EC64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC3DBF6D-73E7-4EA5-9249-52A8873C15F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC3DBF6D-73E7-4EA5-9249-52A8873C15F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5E2509F-FFE9-45BF-B5CD-10F078CD5CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5E2509F-FFE9-45BF-B5CD-10F078CD5CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F4C349D-DA47-4950-A680-E339A02852C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
   <sheets>
     <sheet name="SinglePlot" sheetId="30" state="hidden" r:id="rId1"/>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F4C349D-DA47-4950-A680-E339A02852C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9087CA1B-66C6-4CB0-B2E8-501ED527FB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
   <sheets>
     <sheet name="SinglePlot" sheetId="30" state="hidden" r:id="rId1"/>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9087CA1B-66C6-4CB0-B2E8-501ED527FB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6F620F3-A2EF-441E-B95B-6FE651738853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6F620F3-A2EF-441E-B95B-6FE651738853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{859CF5A4-6B7A-45E2-BA02-91EF99B6DD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
@@ -443,13 +443,13 @@
     <t>xleda Documentation:</t>
   </si>
   <si>
-    <t>https://github.com/InfoDesigner/xleda/</t>
-  </si>
-  <si>
     <t xml:space="preserve">► </t>
   </si>
   <si>
     <t>Overview →</t>
+  </si>
+  <si>
+    <t>https://infodesigner.github.io/xleda/</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1079,7 @@
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
@@ -1405,6 +1405,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="28" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="3" fontId="32" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4818,7 +4821,7 @@
     <row r="1" spans="2:16" ht="5.0999999999999996" customHeight="1"/>
     <row r="2" spans="2:16" ht="20.100000000000001" customHeight="1">
       <c r="B2" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="81"/>
     </row>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="6" spans="1:28" ht="15" customHeight="1">
       <c r="B6" s="113" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="114" t="s">
         <v>93</v>
@@ -4961,10 +4964,10 @@
       <c r="K8" s="43"/>
     </row>
     <row r="9" spans="1:28" ht="30" hidden="1" customHeight="1">
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="118" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="117"/>
+      <c r="D9" s="118"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -4972,8 +4975,8 @@
     </row>
     <row r="10" spans="1:28" ht="15" hidden="1" customHeight="1">
       <c r="C10" s="43"/>
-      <c r="D10" s="80" t="s">
-        <v>105</v>
+      <c r="D10" s="117" t="s">
+        <v>107</v>
       </c>
       <c r="E10" s="43"/>
       <c r="F10" s="43"/>
@@ -4990,10 +4993,10 @@
     </row>
     <row r="12" spans="1:28" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="117"/>
+      <c r="D12" s="118"/>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
       <c r="K12" s="43"/>
@@ -5047,10 +5050,10 @@
       <c r="L19" s="38"/>
     </row>
     <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="117"/>
+      <c r="D20" s="118"/>
       <c r="E20" s="78"/>
       <c r="L20" s="38"/>
     </row>
@@ -5178,10 +5181,10 @@
       <c r="Y38" s="38"/>
     </row>
     <row r="39" spans="2:25" ht="30" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="C39" s="117" t="s">
+      <c r="C39" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="117"/>
+      <c r="D39" s="118"/>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
       <c r="H39" s="43"/>
@@ -5402,7 +5405,7 @@
     <row r="55" spans="1:31" ht="15" customHeight="1" collapsed="1">
       <c r="A55" s="6"/>
       <c r="B55" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>86</v>
@@ -5460,7 +5463,7 @@
     </row>
     <row r="61" spans="1:31" ht="15" customHeight="1">
       <c r="B61" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>87</v>
@@ -5738,7 +5741,7 @@
     <row r="7" spans="1:8">
       <c r="A7" s="116"/>
       <c r="B7" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
@@ -5841,7 +5844,7 @@
     <row r="23" spans="1:6" outlineLevel="1">
       <c r="A23" s="116"/>
       <c r="B23" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
@@ -5930,7 +5933,7 @@
     <row r="36" spans="1:6" outlineLevel="1" collapsed="1">
       <c r="A36" s="116"/>
       <c r="B36" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>16</v>
@@ -5992,7 +5995,7 @@
     <row r="46" spans="1:6" outlineLevel="1" collapsed="1">
       <c r="A46" s="116"/>
       <c r="B46" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>22</v>
@@ -6085,7 +6088,7 @@
     <row r="58" spans="1:6" outlineLevel="1" collapsed="1">
       <c r="A58" s="116"/>
       <c r="B58" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>27</v>
@@ -6217,7 +6220,7 @@
     <row r="69" spans="1:6" outlineLevel="1" collapsed="1">
       <c r="A69" s="116"/>
       <c r="B69" s="82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>36</v>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{859CF5A4-6B7A-45E2-BA02-91EF99B6DD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1667CC2A-BDD0-4920-8BE1-707D24FA4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1667CC2A-BDD0-4920-8BE1-707D24FA4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B5D9F2D-52D1-4600-A867-145EC2DB8A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
   <sheets>
     <sheet name="SinglePlot" sheetId="30" state="hidden" r:id="rId1"/>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\.xleda\src\xleda\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1667CC2A-BDD0-4920-8BE1-707D24FA4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DFCBA43-1AEB-42AF-AF76-ECA985144494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
   <sheets>
     <sheet name="SinglePlot" sheetId="30" state="hidden" r:id="rId1"/>
